--- a/data/normalized/basidiospore_filled.xlsx
+++ b/data/normalized/basidiospore_filled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hensley/Desktop/wiscam_microscopy/data/normalized/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_CE5FCEF7B23C5722D1793A95395BDA16E646BBFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_EC832DEA99DC10123B9A2C95395BDA16E6461BEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="860" windowWidth="29400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2040,6 +2040,42 @@
       <c r="C23" t="s">
         <v>57</v>
       </c>
+      <c r="D23">
+        <v>25</v>
+      </c>
+      <c r="E23">
+        <v>8</v>
+      </c>
+      <c r="F23">
+        <v>8.5</v>
+      </c>
+      <c r="G23">
+        <v>10.5</v>
+      </c>
+      <c r="H23">
+        <v>12</v>
+      </c>
+      <c r="I23">
+        <v>8</v>
+      </c>
+      <c r="J23">
+        <v>8</v>
+      </c>
+      <c r="K23">
+        <v>10.5</v>
+      </c>
+      <c r="L23">
+        <v>11.5</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1.0244529247244281</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
@@ -2645,6 +2681,42 @@
       <c r="C42" t="s">
         <v>38</v>
       </c>
+      <c r="D42">
+        <v>11</v>
+      </c>
+      <c r="E42">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <v>11</v>
+      </c>
+      <c r="G42">
+        <v>13</v>
+      </c>
+      <c r="H42">
+        <v>13.5</v>
+      </c>
+      <c r="I42">
+        <v>8</v>
+      </c>
+      <c r="J42">
+        <v>8</v>
+      </c>
+      <c r="K42">
+        <v>9.5</v>
+      </c>
+      <c r="L42">
+        <v>10</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>1.3708106607874411</v>
+      </c>
+      <c r="O42">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
@@ -2987,6 +3059,42 @@
       <c r="C60" t="s">
         <v>109</v>
       </c>
+      <c r="D60">
+        <v>13</v>
+      </c>
+      <c r="E60">
+        <v>15.5</v>
+      </c>
+      <c r="F60">
+        <v>16.5</v>
+      </c>
+      <c r="G60">
+        <v>18</v>
+      </c>
+      <c r="H60">
+        <v>20</v>
+      </c>
+      <c r="I60">
+        <v>12.5</v>
+      </c>
+      <c r="J60">
+        <v>12.5</v>
+      </c>
+      <c r="K60">
+        <v>14</v>
+      </c>
+      <c r="L60">
+        <v>14.5</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>1.3032816971809009</v>
+      </c>
+      <c r="O60">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
@@ -3030,6 +3138,42 @@
       </c>
       <c r="C64" t="s">
         <v>28</v>
+      </c>
+      <c r="D64">
+        <v>22</v>
+      </c>
+      <c r="E64">
+        <v>9.5</v>
+      </c>
+      <c r="F64">
+        <v>10</v>
+      </c>
+      <c r="G64">
+        <v>12.5</v>
+      </c>
+      <c r="H64">
+        <v>13</v>
+      </c>
+      <c r="I64">
+        <v>9.5</v>
+      </c>
+      <c r="J64">
+        <v>10</v>
+      </c>
+      <c r="K64">
+        <v>11.5</v>
+      </c>
+      <c r="L64">
+        <v>12</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+      <c r="N64">
+        <v>1.070212226577943</v>
+      </c>
+      <c r="O64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
@@ -4048,16 +4192,16 @@
         <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -4068,16 +4212,16 @@
         <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -4168,16 +4312,16 @@
         <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -4408,16 +4552,16 @@
         <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">

--- a/data/normalized/basidiospore_filled.xlsx
+++ b/data/normalized/basidiospore_filled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hensley/Desktop/wiscam_microscopy/data/normalized/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_EC832DEA99DC10123B9A2C95395BDA16E6461BEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_E157CCF903D49943B3F93495395BDA16E64663FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="860" windowWidth="29400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="219">
   <si>
     <t>specimen_id</t>
   </si>
@@ -524,6 +524,18 @@
     <t>30293</t>
   </si>
   <si>
+    <t>30295</t>
+  </si>
+  <si>
+    <t>Amanita banningiana</t>
+  </si>
+  <si>
+    <t>30300</t>
+  </si>
+  <si>
+    <t>Amanita firma</t>
+  </si>
+  <si>
     <t>40220</t>
   </si>
   <si>
@@ -660,6 +672,12 @@
   </si>
   <si>
     <t>ok</t>
+  </si>
+  <si>
+    <t>30211(immature)</t>
+  </si>
+  <si>
+    <t>30210(not found)</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q145"/>
+  <dimension ref="A1:Q147"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -1120,7 +1138,7 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>1.0950696320018529</v>
+        <v>1.095069632001854</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -2040,42 +2058,6 @@
       <c r="C23" t="s">
         <v>57</v>
       </c>
-      <c r="D23">
-        <v>25</v>
-      </c>
-      <c r="E23">
-        <v>8</v>
-      </c>
-      <c r="F23">
-        <v>8.5</v>
-      </c>
-      <c r="G23">
-        <v>10.5</v>
-      </c>
-      <c r="H23">
-        <v>12</v>
-      </c>
-      <c r="I23">
-        <v>8</v>
-      </c>
-      <c r="J23">
-        <v>8</v>
-      </c>
-      <c r="K23">
-        <v>10.5</v>
-      </c>
-      <c r="L23">
-        <v>11.5</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23">
-        <v>1.0244529247244281</v>
-      </c>
-      <c r="O23">
-        <v>1</v>
-      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
@@ -2681,42 +2663,6 @@
       <c r="C42" t="s">
         <v>38</v>
       </c>
-      <c r="D42">
-        <v>11</v>
-      </c>
-      <c r="E42">
-        <v>11</v>
-      </c>
-      <c r="F42">
-        <v>11</v>
-      </c>
-      <c r="G42">
-        <v>13</v>
-      </c>
-      <c r="H42">
-        <v>13.5</v>
-      </c>
-      <c r="I42">
-        <v>8</v>
-      </c>
-      <c r="J42">
-        <v>8</v>
-      </c>
-      <c r="K42">
-        <v>9.5</v>
-      </c>
-      <c r="L42">
-        <v>10</v>
-      </c>
-      <c r="M42">
-        <v>1</v>
-      </c>
-      <c r="N42">
-        <v>1.3708106607874411</v>
-      </c>
-      <c r="O42">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
@@ -3059,42 +3005,6 @@
       <c r="C60" t="s">
         <v>109</v>
       </c>
-      <c r="D60">
-        <v>13</v>
-      </c>
-      <c r="E60">
-        <v>15.5</v>
-      </c>
-      <c r="F60">
-        <v>16.5</v>
-      </c>
-      <c r="G60">
-        <v>18</v>
-      </c>
-      <c r="H60">
-        <v>20</v>
-      </c>
-      <c r="I60">
-        <v>12.5</v>
-      </c>
-      <c r="J60">
-        <v>12.5</v>
-      </c>
-      <c r="K60">
-        <v>14</v>
-      </c>
-      <c r="L60">
-        <v>14.5</v>
-      </c>
-      <c r="M60">
-        <v>1</v>
-      </c>
-      <c r="N60">
-        <v>1.3032816971809009</v>
-      </c>
-      <c r="O60">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
@@ -3139,42 +3049,6 @@
       <c r="C64" t="s">
         <v>28</v>
       </c>
-      <c r="D64">
-        <v>22</v>
-      </c>
-      <c r="E64">
-        <v>9.5</v>
-      </c>
-      <c r="F64">
-        <v>10</v>
-      </c>
-      <c r="G64">
-        <v>12.5</v>
-      </c>
-      <c r="H64">
-        <v>13</v>
-      </c>
-      <c r="I64">
-        <v>9.5</v>
-      </c>
-      <c r="J64">
-        <v>10</v>
-      </c>
-      <c r="K64">
-        <v>11.5</v>
-      </c>
-      <c r="L64">
-        <v>12</v>
-      </c>
-      <c r="M64">
-        <v>1</v>
-      </c>
-      <c r="N64">
-        <v>1.070212226577943</v>
-      </c>
-      <c r="O64">
-        <v>1</v>
-      </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
@@ -3186,6 +3060,42 @@
       <c r="C65" t="s">
         <v>28</v>
       </c>
+      <c r="D65">
+        <v>25</v>
+      </c>
+      <c r="E65">
+        <v>8.5</v>
+      </c>
+      <c r="F65">
+        <v>10</v>
+      </c>
+      <c r="G65">
+        <v>11.5</v>
+      </c>
+      <c r="H65">
+        <v>12</v>
+      </c>
+      <c r="I65">
+        <v>10</v>
+      </c>
+      <c r="J65">
+        <v>10</v>
+      </c>
+      <c r="K65">
+        <v>12.5</v>
+      </c>
+      <c r="L65">
+        <v>13</v>
+      </c>
+      <c r="M65">
+        <v>1</v>
+      </c>
+      <c r="N65">
+        <v>0.96383355195529108</v>
+      </c>
+      <c r="O65">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
@@ -3219,6 +3129,42 @@
       <c r="C68" t="s">
         <v>57</v>
       </c>
+      <c r="D68">
+        <v>25</v>
+      </c>
+      <c r="E68">
+        <v>7</v>
+      </c>
+      <c r="F68">
+        <v>7.5</v>
+      </c>
+      <c r="G68">
+        <v>9</v>
+      </c>
+      <c r="H68">
+        <v>9.5</v>
+      </c>
+      <c r="I68">
+        <v>7</v>
+      </c>
+      <c r="J68">
+        <v>7</v>
+      </c>
+      <c r="K68">
+        <v>8.5</v>
+      </c>
+      <c r="L68">
+        <v>9</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>1.0439005602240901</v>
+      </c>
+      <c r="O68">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
@@ -3388,7 +3334,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>134</v>
       </c>
@@ -3399,7 +3345,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>135</v>
       </c>
@@ -3410,7 +3356,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>137</v>
       </c>
@@ -3421,7 +3367,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>138</v>
       </c>
@@ -3432,7 +3378,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>139</v>
       </c>
@@ -3443,7 +3389,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>140</v>
       </c>
@@ -3454,7 +3400,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>141</v>
       </c>
@@ -3465,7 +3411,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>143</v>
       </c>
@@ -3476,7 +3422,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>144</v>
       </c>
@@ -3487,7 +3433,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>145</v>
       </c>
@@ -3498,7 +3444,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>147</v>
       </c>
@@ -3509,7 +3455,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>148</v>
       </c>
@@ -3520,7 +3466,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>149</v>
       </c>
@@ -3530,8 +3476,44 @@
       <c r="C93" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D93">
+        <v>25</v>
+      </c>
+      <c r="E93">
+        <v>11</v>
+      </c>
+      <c r="F93">
+        <v>11</v>
+      </c>
+      <c r="G93">
+        <v>13.5</v>
+      </c>
+      <c r="H93">
+        <v>14.5</v>
+      </c>
+      <c r="I93">
+        <v>6.5</v>
+      </c>
+      <c r="J93">
+        <v>7</v>
+      </c>
+      <c r="K93">
+        <v>9</v>
+      </c>
+      <c r="L93">
+        <v>9</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>1.5041826474179421</v>
+      </c>
+      <c r="O93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>150</v>
       </c>
@@ -3542,7 +3524,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>151</v>
       </c>
@@ -3552,8 +3534,44 @@
       <c r="C95" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D95">
+        <v>25</v>
+      </c>
+      <c r="E95">
+        <v>10</v>
+      </c>
+      <c r="F95">
+        <v>11</v>
+      </c>
+      <c r="G95">
+        <v>14</v>
+      </c>
+      <c r="H95">
+        <v>14.5</v>
+      </c>
+      <c r="I95">
+        <v>6</v>
+      </c>
+      <c r="J95">
+        <v>6.5</v>
+      </c>
+      <c r="K95">
+        <v>8.5</v>
+      </c>
+      <c r="L95">
+        <v>9</v>
+      </c>
+      <c r="M95">
+        <v>1.5</v>
+      </c>
+      <c r="N95">
+        <v>1.6309453063276591</v>
+      </c>
+      <c r="O95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>152</v>
       </c>
@@ -3564,7 +3582,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>153</v>
       </c>
@@ -3575,7 +3593,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>155</v>
       </c>
@@ -3586,7 +3604,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>156</v>
       </c>
@@ -3597,7 +3615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>157</v>
       </c>
@@ -3608,7 +3626,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>158</v>
       </c>
@@ -3619,7 +3637,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>159</v>
       </c>
@@ -3630,7 +3648,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>160</v>
       </c>
@@ -3641,7 +3659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>161</v>
       </c>
@@ -3652,7 +3670,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>162</v>
       </c>
@@ -3663,7 +3681,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>163</v>
       </c>
@@ -3674,7 +3692,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>165</v>
       </c>
@@ -3685,7 +3703,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>166</v>
       </c>
@@ -3696,67 +3714,139 @@
         <v>57</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>167</v>
       </c>
       <c r="B109" t="s">
+        <v>168</v>
+      </c>
+      <c r="C109" t="s">
+        <v>109</v>
+      </c>
+      <c r="D109">
+        <v>25</v>
+      </c>
+      <c r="E109">
+        <v>9.5</v>
+      </c>
+      <c r="F109">
+        <v>9.5</v>
+      </c>
+      <c r="G109">
+        <v>11.5</v>
+      </c>
+      <c r="H109">
+        <v>12</v>
+      </c>
+      <c r="I109">
+        <v>6.5</v>
+      </c>
+      <c r="J109">
+        <v>6.5</v>
+      </c>
+      <c r="K109">
+        <v>8</v>
+      </c>
+      <c r="L109">
+        <v>8.5</v>
+      </c>
+      <c r="M109">
+        <v>1.5</v>
+      </c>
+      <c r="N109">
+        <v>1.449987071751778</v>
+      </c>
+      <c r="O109">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>169</v>
+      </c>
+      <c r="B110" t="s">
+        <v>170</v>
+      </c>
+      <c r="C110" t="s">
+        <v>72</v>
+      </c>
+      <c r="D110">
+        <v>25</v>
+      </c>
+      <c r="E110">
+        <v>11.5</v>
+      </c>
+      <c r="F110">
+        <v>12.5</v>
+      </c>
+      <c r="G110">
+        <v>15</v>
+      </c>
+      <c r="H110">
+        <v>16</v>
+      </c>
+      <c r="I110">
+        <v>4</v>
+      </c>
+      <c r="J110">
+        <v>4</v>
+      </c>
+      <c r="K110">
+        <v>5</v>
+      </c>
+      <c r="L110">
+        <v>5</v>
+      </c>
+      <c r="M110">
+        <v>2.5</v>
+      </c>
+      <c r="N110">
+        <v>2.939777777777778</v>
+      </c>
+      <c r="O110">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>171</v>
+      </c>
+      <c r="B111" t="s">
         <v>66</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C111" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>168</v>
-      </c>
-      <c r="B110" t="s">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>172</v>
+      </c>
+      <c r="B112" t="s">
         <v>21</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C112" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>169</v>
-      </c>
-      <c r="B111" t="s">
-        <v>21</v>
-      </c>
-      <c r="C111" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>170</v>
-      </c>
-      <c r="B112" t="s">
-        <v>43</v>
-      </c>
-      <c r="C112" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B113" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C113" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B114" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C114" t="s">
         <v>28</v>
@@ -3764,29 +3854,29 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B115" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C115" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B116" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C116" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B117" t="s">
         <v>53</v>
@@ -3797,7 +3887,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B118" t="s">
         <v>53</v>
@@ -3808,7 +3898,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B119" t="s">
         <v>53</v>
@@ -3819,7 +3909,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B120" t="s">
         <v>53</v>
@@ -3830,40 +3920,40 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B121" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C121" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B122" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="C122" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B123" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="C123" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B124" t="s">
         <v>85</v>
@@ -3874,10 +3964,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B125" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C125" t="s">
         <v>38</v>
@@ -3885,29 +3975,29 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B126" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C126" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B127" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C127" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B128" t="s">
         <v>96</v>
@@ -3918,7 +4008,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B129" t="s">
         <v>96</v>
@@ -3929,7 +4019,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B130" t="s">
         <v>96</v>
@@ -3940,7 +4030,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B131" t="s">
         <v>96</v>
@@ -3951,7 +4041,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B132" t="s">
         <v>96</v>
@@ -3962,65 +4052,65 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B133" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C133" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B134" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C134" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B135" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C135" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B136" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="C136" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B137" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="C137" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B138" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="C138" t="s">
         <v>28</v>
@@ -4028,18 +4118,18 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B139" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="C139" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B140" t="s">
         <v>89</v>
@@ -4050,7 +4140,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B141" t="s">
         <v>89</v>
@@ -4061,7 +4151,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B142" t="s">
         <v>89</v>
@@ -4072,7 +4162,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B143" t="s">
         <v>89</v>
@@ -4083,15 +4173,37 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+      <c r="B144" t="s">
+        <v>89</v>
+      </c>
+      <c r="C144" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B145" t="s">
-        <v>203</v>
+        <v>89</v>
+      </c>
+      <c r="C145" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>206</v>
+      </c>
+      <c r="B147" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -4101,7 +4213,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -4109,19 +4221,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -4129,10 +4241,10 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -4146,13 +4258,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -4166,173 +4278,173 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="C7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="C8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="C9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D10">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="C11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D12">
         <v>25</v>
@@ -4346,13 +4458,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D13">
         <v>25</v>
@@ -4366,73 +4478,73 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="C14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D16">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D17">
         <v>25</v>
@@ -4446,13 +4558,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D18">
         <v>25</v>
@@ -4466,73 +4578,73 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D22">
         <v>25</v>
@@ -4546,33 +4658,33 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D23">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D24">
         <v>25</v>
@@ -4586,13 +4698,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D25">
         <v>25</v>
@@ -4606,53 +4718,53 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D26">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F26">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D27">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D28">
         <v>25</v>
@@ -4666,13 +4778,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D29">
         <v>25</v>
@@ -4686,13 +4798,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D30">
         <v>25</v>
@@ -4706,13 +4818,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D31">
         <v>25</v>
@@ -4726,53 +4838,53 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>217</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>217</v>
       </c>
       <c r="C32" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D32">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="C33" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D33">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D34">
         <v>25</v>
@@ -4786,13 +4898,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D35">
         <v>25</v>
@@ -4806,33 +4918,33 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E36">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F36">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D37">
         <v>25</v>
@@ -4846,13 +4958,13 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C38" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D38">
         <v>25</v>
@@ -4866,13 +4978,13 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D39">
         <v>25</v>
@@ -4886,13 +4998,13 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D40">
         <v>25</v>
@@ -4906,33 +5018,33 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D41">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D42">
         <v>25</v>
@@ -4946,21 +5058,381 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>216</v>
+      </c>
+      <c r="D43">
+        <v>25</v>
+      </c>
+      <c r="E43">
+        <v>25</v>
+      </c>
+      <c r="F43">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44">
+        <v>25</v>
+      </c>
+      <c r="E44">
+        <v>25</v>
+      </c>
+      <c r="F44">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" t="s">
+        <v>216</v>
+      </c>
+      <c r="D45">
+        <v>25</v>
+      </c>
+      <c r="E45">
+        <v>25</v>
+      </c>
+      <c r="F45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" t="s">
+        <v>216</v>
+      </c>
+      <c r="D46">
+        <v>25</v>
+      </c>
+      <c r="E46">
+        <v>25</v>
+      </c>
+      <c r="F46">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
+        <v>216</v>
+      </c>
+      <c r="D47">
+        <v>25</v>
+      </c>
+      <c r="E47">
+        <v>25</v>
+      </c>
+      <c r="F47">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" t="s">
+        <v>216</v>
+      </c>
+      <c r="D48">
+        <v>25</v>
+      </c>
+      <c r="E48">
+        <v>25</v>
+      </c>
+      <c r="F48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" t="s">
+        <v>216</v>
+      </c>
+      <c r="D49">
+        <v>25</v>
+      </c>
+      <c r="E49">
+        <v>25</v>
+      </c>
+      <c r="F49">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" t="s">
+        <v>216</v>
+      </c>
+      <c r="D50">
+        <v>25</v>
+      </c>
+      <c r="E50">
+        <v>25</v>
+      </c>
+      <c r="F50">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" t="s">
+        <v>216</v>
+      </c>
+      <c r="D51">
+        <v>25</v>
+      </c>
+      <c r="E51">
+        <v>25</v>
+      </c>
+      <c r="F51">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" t="s">
+        <v>216</v>
+      </c>
+      <c r="D52">
+        <v>25</v>
+      </c>
+      <c r="E52">
+        <v>25</v>
+      </c>
+      <c r="F52">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" t="s">
+        <v>34</v>
+      </c>
+      <c r="C53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D53">
+        <v>25</v>
+      </c>
+      <c r="E53">
+        <v>25</v>
+      </c>
+      <c r="F53">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>32</v>
+      </c>
+      <c r="B54" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" t="s">
+        <v>216</v>
+      </c>
+      <c r="D54">
+        <v>13</v>
+      </c>
+      <c r="E54">
+        <v>13</v>
+      </c>
+      <c r="F54">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" t="s">
+        <v>216</v>
+      </c>
+      <c r="D55">
+        <v>25</v>
+      </c>
+      <c r="E55">
+        <v>25</v>
+      </c>
+      <c r="F55">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>29</v>
+      </c>
+      <c r="B56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" t="s">
+        <v>216</v>
+      </c>
+      <c r="D56">
+        <v>25</v>
+      </c>
+      <c r="E56">
+        <v>25</v>
+      </c>
+      <c r="F56">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>26</v>
+      </c>
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>216</v>
+      </c>
+      <c r="D57">
+        <v>25</v>
+      </c>
+      <c r="E57">
+        <v>25</v>
+      </c>
+      <c r="F57">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
+        <v>216</v>
+      </c>
+      <c r="D58">
+        <v>25</v>
+      </c>
+      <c r="E58">
+        <v>25</v>
+      </c>
+      <c r="F58">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" t="s">
+        <v>216</v>
+      </c>
+      <c r="D59">
+        <v>25</v>
+      </c>
+      <c r="E59">
+        <v>25</v>
+      </c>
+      <c r="F59">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" t="s">
+        <v>216</v>
+      </c>
+      <c r="D60">
+        <v>25</v>
+      </c>
+      <c r="E60">
+        <v>25</v>
+      </c>
+      <c r="F60">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
         <v>17</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B61" t="s">
         <v>17</v>
       </c>
-      <c r="C43" t="s">
-        <v>212</v>
-      </c>
-      <c r="D43">
-        <v>25</v>
-      </c>
-      <c r="E43">
-        <v>25</v>
-      </c>
-      <c r="F43">
+      <c r="C61" t="s">
+        <v>216</v>
+      </c>
+      <c r="D61">
+        <v>25</v>
+      </c>
+      <c r="E61">
+        <v>25</v>
+      </c>
+      <c r="F61">
         <v>25</v>
       </c>
     </row>
